--- a/build/simple-flow-v2/testrail-import/Simple-Flow-V2_testrail-import.xlsx
+++ b/build/simple-flow-v2/testrail-import/Simple-Flow-V2_testrail-import.xlsx
@@ -518,7 +518,7 @@
 2. The page is grouped into "Workflow", "Line requirements" and "Parts", separated by dividers.
 3. Every label reads in the "Require..." form, so turning one on always means more work.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -571,7 +571,7 @@
 2. The new wording is the opposite of the stored value: auto-pick off means picking required. The rename is a deliberate inversion, not just a text change.
 3. The shop keeps exactly the picking behaviour it had before the rename.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -624,7 +624,7 @@
 2. When on, an Order action appears on each qualifying part and in the bulk bar; when off, parts are recorded as ordered automatically and no Order action appears anywhere.
 3. Because it defaults to on and nothing orders parts automatically today, an upgraded shop sees no change.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -676,7 +676,7 @@
 2. Require receiving on: outstanding parts block the work order from being invoiced, and a Receive button sits on each part row. Off: outstanding parts do not block invoicing, and Receive moves into the part's ... menu.
 3. Both default to on (their behaviour today).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -728,7 +728,7 @@
 2. Switching Require picking on later does not un-pick anything; parts already picked stay picked.
 3. No shop's behaviour changes at the moment this ships.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9247 (Story 1, Work Order settings page) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -785,7 +785,7 @@
 5. Require approval off: every line in Needs Approval becomes Approved (turning an estimate into approved work). On: lines already approved stay approved.
 6. Statuses change in the underlying records, not only in the interface; invoicing checks the same state.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9248 (Story 2, Settings apply to every work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9248 (Story 2, Settings apply to every work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -836,7 +836,7 @@
           <t xml:space="preserve">1. Every record changed is written to the audit log — on the work order and on each line or part changed.
 2. Each entry is attributed to the system and names the cause, for example "Line approved because Require approval for new lines was turned off".
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9248 (Story 2, Settings apply to every work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9248 (Story 2, Settings apply to every work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -889,7 +889,7 @@
 3. No settings change marks anything as received (receiving needs a vendor bill only a person can supply).
 4. If the run fails part way, re-running finishes the remainder without repeating what was already done.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9248 (Story 2, Settings apply to every work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9248 (Story 2, Settings apply to every work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -942,7 +942,7 @@
 4. The two money/commitment consequences — turning receiving on and turning approval off — are stated as a warning, not a count alone.
 5. When the affected count is large, the confirmation also advises making the change outside working hours and states the app will be unavailable while it runs.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9249 (Story 3, Confirmation before a settings change) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9249 (Story 3, Confirmation before a settings change) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -992,7 +992,7 @@
         <is>
           <t xml:space="preserve">1. Cancelling leaves the setting as it was and changes no records.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9249 (Story 3, Confirmation before a settings change) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9249 (Story 3, Confirmation before a settings change) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1043,7 +1043,7 @@
           <t xml:space="preserve">1. While the change is applied the app shows a blocking indicator and the user cannot act on the affected data.
 2. The user is not returned to the settings page until every affected record has been changed.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9250 (Story 4, Applying a settings change at scale) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9250 (Story 4, Applying a settings change at scale) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1094,7 +1094,7 @@
           <t xml:space="preserve">1. A partially applied change is never left visible.
 2. If the run fails, either the change completes or the setting reverts, and the user is told which.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9250 (Story 4, Applying a settings change at scale) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9250 (Story 4, Applying a settings change at scale) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1149,7 +1149,7 @@
 4. Receiving required, part ordered but not received: the line completes; the work order cannot be invoiced until that part is received or deferred with Received later.
 5. Completing a line changes nothing about its parts — they keep whatever status the settings gave them.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1201,7 +1201,7 @@
 2. Where receiving is not required, an unresolved core is asked before the line completes (such a part may never pass through a receive and the invoice must still be right).
 3. Satisfying the last outstanding requirement makes a line completable — it does not complete it by itself.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1255,7 +1255,7 @@
 2. Nothing else completes a line — no timer and no background job.
 3. Mark as reviewed is NOT on that list: it becomes available only once every line is already complete, so there is never an open line for it to close.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1308,7 +1308,7 @@
 3. If a tech story is required and empty, it is required at clock out.
 4. The clock-out modal is otherwise unchanged.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1361,7 +1361,7 @@
 2. A line reopened after completion returns to Approved with its parts unchanged.
 3. A Technician in Tech View cannot complete (they cannot approve), but can still pick parts.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9251 (Story 5, Parts no longer block completing a line) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1416,7 +1416,7 @@
 5. Any action not listed for a status is not visible, on the line or in the bulk action bar.
 6. Complete is not offered on a Needs Approval line and Approve is not offered on an already-Approved line (both do nothing).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1466,7 +1466,7 @@
           <t xml:space="preserve">1. Decline stays visible but is disabled while the line holds parts that were received or picked.
 2. The disabled reason reads "Return this line's received parts before declining it".
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1520,7 +1520,7 @@
 5. Received later: nothing on the row, Receive in the ... menu.
 6. Received or picked: nothing (finished). Returned: nothing (sent back, stays visible on the line and in returns).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1572,7 +1572,7 @@
 2. With receiving not required, Receive moves from the part row into the part's ... menu - it is never removed outright.
 3. Ordering a Requested part only does something when the part is vendor-sourced (including a vendorless part marked Vendor missing); an inventory/found part or one with no source needs its details completed first.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1626,7 +1626,7 @@
 4. Declining a line does not remove its parts from a purchase order (only deleting a part does that).
 5. A part action the user's role does not carry is absent even when the part's state qualifies (Pick follows Pick Parts, Order follows Order Parts).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9252 (Story 6, Which actions appear on a line and on a part) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1680,7 +1680,7 @@
 4. Each action follows one rule: nothing in the selection qualifies -&gt; hidden; something qualifies but is blocked -&gt; shown disabled with the reason; qualifies and not blocked -&gt; shown with its count.
 5. Line actions count lines and parts actions count parts ("Receive 5 parts" may come from two lines); a count never includes what the action would skip.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9253 (Story 7, The bulk action bar) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9253 (Story 7, The bulk action bar) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1730,10 +1730,10 @@
         <is>
           <t xml:space="preserve">1. Primary slots fill in this order and do not change as parts progress: the finish action (when the selection covers every open line), then Complete lines, then Approve, then the parts actions as Order, Receive, Pick.
 2. Decline is always in More, never in a primary slot.
-3. More contains, in order: Authorization required, Split to new work order, Create invoice, Decline.
+3. More contains, in order: Authorization required, Split to new work order, Decline. Create invoice is not enumerated in this ordered list; it is described next and disappears once an invoice exists.
 4. Create invoice acts on the whole work order whatever is selected, carries no count, and disappears once an invoice exists.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9253 (Story 7, The bulk action bar) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9253 (Story 7, The bulk action bar) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1787,7 +1787,7 @@
 3. Receiving and picking open their own screens, so they neither confirm nor offer undo.
 4. One toast per bulk action, summarising the result.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9253 (Story 7, The bulk action bar) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9253 (Story 7, The bulk action bar) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1841,7 +1841,7 @@
 4. A selection where nothing applies shows "n selected" and "No actions available for this selection".
 5. Delete lines is not in the bar this release; Mark as reviewed is never in the bulk bar (it acts on the whole work order).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9253 (Story 7, The bulk action bar) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9253 (Story 7, The bulk action bar) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1897,7 +1897,7 @@
 5. The result names each failure with its line number and reason in one message, for example "3 lines approved. 1 line couldn't be declined: Line 3, parts must be returned first".
 6. Undo restores only the lines that changed, to the status they held.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9254 (Story 8, Bulk approve and decline) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9254 (Story 8, Bulk approve and decline) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -1949,7 +1949,7 @@
 2. Lines already in the target status are skipped silently and were never in the count.
 3. A selection made up entirely of declined lines shows no Approve button at all (the count would be zero).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9254 (Story 8, Bulk approve and decline) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9254 (Story 8, Bulk approve and decline) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2004,7 +2004,7 @@
 4. Completing the last open lines stops there - no invoice is created and the user is not navigated anywhere.
 5. With review required, this is the action that makes Mark as reviewed appear (review needs every line complete first).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9255 (Story 9, Bulk complete lines) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9255 (Story 9, Bulk complete lines) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2056,7 +2056,7 @@
 2. Bulk deletion of lines is a documented follow-up (SV-9256), not part of Simple Flow V2.
 3. Single-line delete is unchanged from V1.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9256 (Story 10, Bulk delete lines - out of scope) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9256 (Story 10, Bulk delete lines - out of scope) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2110,7 +2110,7 @@
 4. A part with no vendor is ordered and counted like any other: the PO is created marked Vendor missing and does not sync to QuickBooks until a vendor is assigned.
 5. Ordering asks for confirmation first because a purchase order is a commitment to a supplier and cannot be undone.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9257 (Story 11, Bulk order parts) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9257 (Story 11, Bulk order parts) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2162,7 +2162,7 @@
 2. Only vendor-sourced parts are placed; an inventory/found part or one with no source is skipped and never counted (it is picked instead, or needs its details completed first).
 3. A user without Order Parts does not see the action, in the bulk bar or on the row.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9257 (Story 11, Bulk order parts) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9257 (Story 11, Bulk order parts) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2215,7 +2215,7 @@
 3. Pick is offered whenever a part is In Stock and unpicked, whatever the setting says.
 4. A picked part asks its core question at the moment it is picked, exactly as today (gated by WO Lines: Create &amp; Edit).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9258 (Story 12, Bulk pick parts) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9258 (Story 12, Bulk pick parts) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2264,7 +2264,7 @@
         <is>
           <t xml:space="preserve">1. A user without Pick Parts does not see the Pick action.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9258 (Story 12, Bulk pick parts) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9258 (Story 12, Bulk pick parts) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2321,7 +2321,7 @@
 5. The settings never change what the modal contains (Require receiving only decides where Receive lives and whether outstanding parts block invoicing).
 6. One card per vendor showing vendor name, part count and total; Vendor missing sorts first.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2377,7 +2377,7 @@
 5. Cost is required and may be zero, arriving prefilled from the purchase order; tax is required and may be zero, prefilled from the vendor's tax rate (falling back to zero when nothing derives it).
 6. Quantity received must be greater than zero, may include decimals, and may exceed what was ordered (the excess is shown but not blocked; the PO absorbs it). Changing cost shows a note that the sell price will update.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2431,7 +2431,7 @@
 3. If the vendor is not found the user can create one from here, under the same Vendor &amp; Order Mgmt gate.
 4. The cursor starts in the vendor invoice number field when the vendor is known, and in the vendor field when it is not; tab order is identical in both states.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2484,7 +2484,7 @@
 3. The card says so before the user confirms.
 4. Receiving uses the existing pipeline, so the vendor bill reaches the accounting system as it does today.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2536,7 +2536,7 @@
 2. No money field is ever both hidden and required, which keeps See Financial Data and the receive permission from deadlocking each other.
 3. The user can complete the receive.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2594,7 +2594,7 @@
 5. There is no way to receive without a vendor bill (a user with parts but no paperwork uses Received later).
 6. If the work order is invoiced mid-session, receiving is refused with the reason; the empty state reads "Nothing to receive".
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9259 (Story 13, Receiving from the work order) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2648,7 +2648,7 @@
 4. Each purchase order row shows its number, the work order number and the part count.
 5. Missing-vendor groups carry an amber treatment and a "Vendor missing" label in both states; once resolved they show the vendor name with an edit affordance.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9260 (Story 14, The receive page and PO bulk receive) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9260 (Story 14, The receive page and PO bulk receive) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2704,7 +2704,7 @@
 5. The tax typed here is vendor-side (stored on the vendor bill; feeds what the shop owes suppliers; not the customer's sales tax); it is typed, not calculated, and does not recompute when a cost or quantity changes.
 6. Sell price is shown here and only here, read-only, on every purchase order.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9260 (Story 14, The receive page and PO bulk receive) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9260 (Story 14, The receive page and PO bulk receive) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2759,7 +2759,7 @@
 4. Without See Financial Data the cost, tax, subtotal, total and sell columns are absent (not masked); receiving still works because those fields arrive with a value.
 5. A Vendor &amp; Order Mgmt: View-only user (e.g. Office) can open the page but cannot receive.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9260 (Story 14, The receive page and PO bulk receive) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9260 (Story 14, The receive page and PO bulk receive) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2815,7 +2815,7 @@
 5. It stays receivable later from its ... menu, and receiving it then asks for the invoice number as normal.
 6. Deferring several at once applies straight away with a toast stating how many were deferred; a deferred part keeps counting in the Waiting on Parts column.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9261 (Story 15, Receive later) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9261 (Story 15, Receive later) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2869,7 +2869,7 @@
 3. Received later is never duplicated in the part's ... menu while the split button is showing.
 4. Deferring does not create a vendor bill, move stock or touch the accounting system - it records that the paperwork is outstanding and nothing else.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9261 (Story 15, Receive later) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9261 (Story 15, Receive later) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2924,7 +2924,7 @@
 5. The run records which lines it covers and whether it is heading to an invoice, fixed when the run opens.
 6. A step the user's role cannot perform is not shown; where that step is the only outstanding work, the action fails with the reason instead of opening an empty wizard.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9262 (Story 16, When the completion wizard opens) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9262 (Story 16, When the completion wizard opens) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -2979,7 +2979,7 @@
 5. A finished step shows a tick and becomes read-only; unfinished steps stay clickable so a user can skip ahead and come back.
 6. Resolve cores is unchanged and appears only when a part in the run carries an unresolved core.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9263 (Story 17, The completion wizard) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9263 (Story 17, The completion wizard) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3034,7 +3034,7 @@
 4. The wizard never mentions ordering, even when ordering is required (a part never marked as ordered is included anyway and ordering happens without user action when the parts are received).
 5. Closing the wizard keeps everything already done; reopening shows only what is left.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9263 (Story 17, The completion wizard) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9263 (Story 17, The completion wizard) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3087,7 +3087,7 @@
 2. Complete all lines: every open line complete, a toast, still on the work order; with review required, this is the moment Mark as reviewed appears in the header.
 3. Create invoice: the invoice is created, the Finance tab and the payment screen open.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9263 (Story 17, The completion wizard) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9263 (Story 17, The completion wizard) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3140,7 +3140,7 @@
 2. If someone else finishes the outstanding work mid-run, the wizard closes to the outcome rather than showing an empty step.
 3. A server error mid-step leaves the step open with the entered values intact.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9263 (Story 17, The completion wizard) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9263 (Story 17, The completion wizard) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3200,7 +3200,7 @@
 6. Lines selected: the bulk action bar, whatever the review setting.
 7. Only one finish action is ever on screen, and only ever one the user can actually press.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9264 (Story 18, Create invoice as the finish action) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9264 (Story 18, Create invoice as the finish action) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3255,7 +3255,7 @@
 4. Where a deposit already covers the whole amount the payment screen is skipped, the work order reads Paid, and the user is told the deposit settled the invoice.
 5. Everything that happens today when an invoice is created still happens from every entry point: a deposit applying, an over-payment becoming a credit, the customer being locked, the accounting sync and the snapshot.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9264 (Story 18, Create invoice as the finish action) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9264 (Story 18, Create invoice as the finish action) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3313,7 +3313,7 @@
 5. Once an invoice exists, both actions are gone from the header and the ... menu.
 6. A user who may review but not invoice sees Mark as reviewed then nothing further; a complete-only user sees nothing in the header; a user without See Financial Data does not see Create invoice at all.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9264 (Story 18, Create invoice as the finish action) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9264 (Story 18, Create invoice as the finish action) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3365,7 +3365,7 @@
 2. The line's ... menu contains Request part, Uncomplete line, Add line note, Save as canned line, Edit labour, Receive parts (n) (when receiving is optional and the line has parts waiting), and Authorization required.
 3. Uncomplete is existing behaviour and is already blocked once the work order is invoiced or paid; the same block applies in the bulk action bar so the two cannot drift apart.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9265 (Story 19, Part rows and menus) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9265 (Story 19, Part rows and menus) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3418,7 +3418,7 @@
 2. Uncomplete line appears only on a completed line.
 3. Receive part is absent for a user without Order Parts, whatever the setting.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9265 (Story 19, Part rows and menus) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9265 (Story 19, Part rows and menus) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3471,7 +3471,7 @@
 2. The order shown on the line is the order on the invoice: one stored order is rewritten whenever parts are moved, and the work order, the invoice and the PDF all read it.
 3. Reordering on either side moves the other, and the line numbers move with the rows rather than staying where they were.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9266 (Story 20, Reordering parts on a line) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9266 (Story 20, Reordering parts on a line) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3524,7 +3524,7 @@
 2. Reordering on an invoiced work order is refused.
 3. Where two people reorder at once, the last write wins and the invoice follows what was stored.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9266 (Story 20, Reordering parts on a line) and the Simple Flow V2 specification version 21, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9266 (Story 20, Reordering parts on a line) and the Simple Flow V2 specification version 23, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3577,7 +3577,7 @@
 3. It is off by default in every role and is granted per role.
 4. It is the only atom this release adds; everything else reuses an existing atom.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9267 (Story 21, Permissions on the new surfaces) and the Simple Flow V2 specification version 21, and the permission map SV-8183, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9267 (Story 21, Permissions on the new surfaces) and the Simple Flow V2 specification version 23, and the permission map SV-8183, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3631,7 +3631,7 @@
 5. Marking reviewed follows Review Work Orders; creating the invoice follows Invoicing &amp; Payments: Create &amp; Edit plus See Financial Data.
 6. The bulk version of an action is governed by exactly the same atom as the single version - no bulk action introduces a gate of its own.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9267 (Story 21, Permissions on the new surfaces) and the permission map SV-8183, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9267 (Story 21, Permissions on the new surfaces) and the Simple Flow V2 specification version 23 and the permission map SV-8183, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3683,7 +3683,7 @@
 2. No money field is ever both hidden and required: receiving needs a cost and a tax, both always prefilled, so a user without See Financial Data receives with those fields removed and the existing values standing.
 3. Where a user cannot see money, those fields are removed rather than masked, and no text that reveals a price by implication is rendered (such as a cost-vs-sell warning).
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9267 (Story 21, Permissions on the new surfaces) and the permission map SV-8183, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9267 (Story 21, Permissions on the new surfaces) and the Simple Flow V2 specification version 23 and the permission map SV-8183, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
@@ -3735,7 +3735,7 @@
 2. The values behind a hidden field are not sent to a screen that is not allowed to show them.
 3. Creating a new vendor keeps the existing vendor-management permission wherever it is offered.
 ---
-This is the expected behaviour as per epic SV-8683 and story SV-9267 (Story 21, Permissions on the new surfaces) and the permission map SV-8183, read on 21 August 2026.
+This is the expected behaviour as per epic SV-8683 and story SV-9267 (Story 21, Permissions on the new surfaces) and the Simple Flow V2 specification version 23 and the permission map SV-8183, read on 21 August 2026.
 AUTOMATION: Not available on Build to test Yet - Last checked 8/21/2026
 </t>
         </is>
